--- a/Ejercicio1.xlsx
+++ b/Ejercicio1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anale\OneDrive\Documents\Proyecto_final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC0F52B0-5CC2-4710-8FC7-4C48E78AB0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D703C5D-671B-451F-BDA6-1DE17F60C6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{BD659C77-AB3E-470F-9D27-A4621EB12803}"/>
   </bookViews>
